--- a/فيزياء ترم ثاني.xlsx
+++ b/فيزياء ترم ثاني.xlsx
@@ -7839,7 +7839,7 @@
         <v>49</v>
       </c>
       <c r="K24">
-        <v>92</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25">
@@ -8014,7 +8014,7 @@
         <v>24</v>
       </c>
       <c r="K29">
-        <v>60</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30">
@@ -8084,7 +8084,7 @@
         <v>40</v>
       </c>
       <c r="K31">
-        <v>71</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -8171,7 +8171,7 @@
         <v>40</v>
       </c>
       <c r="K2">
-        <v>54</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3">
@@ -8241,7 +8241,7 @@
         <v>14</v>
       </c>
       <c r="K4">
-        <v>28</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5">
@@ -8276,7 +8276,7 @@
         <v>42</v>
       </c>
       <c r="K5">
-        <v>80</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6">
@@ -8311,7 +8311,7 @@
         <v>20</v>
       </c>
       <c r="K6">
-        <v>34</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7">
@@ -8346,7 +8346,7 @@
         <v>30</v>
       </c>
       <c r="K7">
-        <v>44</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8">
@@ -8451,7 +8451,7 @@
         <v>40</v>
       </c>
       <c r="K10">
-        <v>75</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11">
@@ -8626,7 +8626,7 @@
         <v>10</v>
       </c>
       <c r="K15">
-        <v>41</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16">
@@ -8661,7 +8661,7 @@
         <v>42</v>
       </c>
       <c r="K16">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -8731,7 +8731,7 @@
         <v>10</v>
       </c>
       <c r="K18">
-        <v>18</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19">
